--- a/AAII_Financials/Quarterly/BIRK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIRK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>BIRK</t>
   </si>
@@ -656,289 +656,302 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>822000</v>
+      </c>
+      <c r="E8" s="3">
         <v>712900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>471900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>617600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>745800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>620800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>374500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>508300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>605100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>519200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>334800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>396400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>516600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>429900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>265600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>356200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>412100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>370200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>218500</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>334400</v>
+      </c>
+      <c r="E9" s="3">
         <v>323600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>201000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>256800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>294700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>262400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>148800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>207800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>245200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>226700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>130500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>137200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>197700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>174100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>101700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>128200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>153300</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>487600</v>
+      </c>
+      <c r="E10" s="3">
         <v>389300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>270900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>360700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>451100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>358400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>225700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>300600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>359900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>292500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>204300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>259300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>318800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>255800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>163900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>228000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>258800</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +974,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,55 +1102,58 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E14" s="3">
         <v>4800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-6300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-20600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>17500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>8100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>21700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1147,70 +1167,76 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E15" s="3">
         <v>36700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>35400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19300</v>
       </c>
-      <c r="G15" s="3">
-        <v>33000</v>
-      </c>
       <c r="H15" s="3">
+        <v>33100</v>
+      </c>
+      <c r="I15" s="3">
         <v>29500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>27000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>26600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>26000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>25700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>21900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>21800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>23900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>17000</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>583900</v>
+      </c>
+      <c r="E17" s="3">
         <v>520900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>382400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>481400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>524400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>434000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>295800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>392100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>434100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>370300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>274600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>364400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>378100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>294700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>217400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>266200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>273500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>238200</v>
+      </c>
+      <c r="E18" s="3">
         <v>192000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>89500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>136100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>221400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>186700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>78700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>116200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>171000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>148900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>60300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>138500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>135200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>48200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>90000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>138600</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,180 +1411,187 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>8000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>15400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-11200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-37400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>18400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>32900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-20200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-48800</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>273000</v>
+      </c>
+      <c r="E21" s="3">
         <v>220700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>121100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>140000</v>
       </c>
-      <c r="G21" s="3">
-        <v>265600</v>
-      </c>
       <c r="H21" s="3">
+        <v>265700</v>
+      </c>
+      <c r="I21" s="3">
         <v>219000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>93400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>136200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>193200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>169000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>73100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>82700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>157700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>138700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>37000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>150800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E22" s="3">
         <v>39000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>21500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>30600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>30300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>29500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>39800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>44400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>29100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>32100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>26800</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -1564,132 +1604,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>182800</v>
+      </c>
+      <c r="E23" s="3">
         <v>140300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>81200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>118900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>211000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>161800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>40600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>87300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>118800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>113400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>99700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>80100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-11600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>69900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>89800</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E24" s="3">
         <v>45800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>21900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>59200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>48200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>38800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>36100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>29300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>30800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>26500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>29300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>21300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12800</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E26" s="3">
         <v>94400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>59400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>110100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>151800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>113600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>58500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>80000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>77300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-29900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>68900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>53700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>64200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>60500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>88100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E27" s="3">
         <v>94400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>59400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>110100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>151800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>113600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>58500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>80000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>77300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-29900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>68900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>53700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>64200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>60500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>88100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2189,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-15400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>11200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>37400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-32900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>20200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>48800</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E33" s="3">
         <v>94400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>59400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>110100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>151800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>113600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>58500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>80000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>77300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-29900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>68900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>53700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>64200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>60500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>88100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8400</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E35" s="3">
         <v>94400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>59400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>110100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>151800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>113600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>58500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>80000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>77300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-29900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>68900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>53700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>64200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>60500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>88100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8400</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,53 +2571,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>792500</v>
+      </c>
+      <c r="E41" s="3">
         <v>232300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>269100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>386100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>307500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>254400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>309100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>396900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>433200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>189600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>187200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>364500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>316200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>186500</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,8 +2634,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,53 +2699,56 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>328400</v>
+      </c>
+      <c r="E43" s="3">
         <v>349200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>143800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>222200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>303700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>291800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>95100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>158700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>225500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>226500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>99000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>125100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>182800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>201200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2671,53 +2764,56 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>963500</v>
+      </c>
+      <c r="E44" s="3">
         <v>973900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>976800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>826500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>789700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>756400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>745000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>696900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>663400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>702300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>712200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>629900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>624000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>639300</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,53 +2829,56 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E45" s="3">
         <v>74800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>72500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>36600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>76200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>47600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>54100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>36200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,53 +2894,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2155000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1630200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1462200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1496400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1477100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1350200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1203400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1297400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1357600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1160500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1040500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1143700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1161900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1063200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,8 +2959,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2904,8 +3009,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -2919,53 +3024,56 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>717500</v>
+      </c>
+      <c r="E48" s="3">
         <v>691400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>668900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>630400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>607500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>551900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>520000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>546700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>509400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>504900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>490300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>432900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>424000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>379500</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,55 +3089,58 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3559200</v>
+      </c>
+      <c r="E49" s="3">
         <v>3582900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3616500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3624900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3640800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3496900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3422700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3562400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3495700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3510100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3565800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3492400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3566800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3566000</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>0</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,53 +3284,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E52" s="3">
         <v>28600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>46200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>33400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>36300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>35800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>41700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>39900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>54600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>57500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>40500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3229,8 +3349,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,53 +3414,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6470500</v>
+      </c>
+      <c r="E54" s="3">
         <v>5954600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5811500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5798600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5762900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5431800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5181900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5448300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5402600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5230100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5154100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5109500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5189400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5036000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3479,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,53 +3531,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200500</v>
+      </c>
+      <c r="E57" s="3">
         <v>163900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>135900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>84600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>185200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>139000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>120900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>83300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>157300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>130900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>115200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>84200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>151800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>115600</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,55 +3594,58 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E58" s="3">
         <v>85800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>71000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>71600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>68000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>83100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>87000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>73800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>61200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>72000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>61500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>75400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>61400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>74100</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3525,53 +3659,56 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>247500</v>
+      </c>
+      <c r="E59" s="3">
         <v>264300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>231000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>320400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>240300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>187500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>190800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>296700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>210300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>168500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>150000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>185100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>162300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>134200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,53 +3724,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>569700</v>
+      </c>
+      <c r="E60" s="3">
         <v>553400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>466900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>532300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>531400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>441500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>423500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>499500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>466300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>404300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>352200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>400700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>410700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>353800</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3649,53 +3789,56 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2133700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1505700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1512000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1498700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1538600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1425800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1375700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1464600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1568400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1551400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1566400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2030800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2072700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2082700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3711,53 +3854,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>353600</v>
+      </c>
+      <c r="E62" s="3">
         <v>352700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>372700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>365200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>400800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>377100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>383700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>395000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>386300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>380100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>375500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6200</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3773,8 +3919,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,53 +4114,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3269300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2618800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2556900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2604000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2671400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2413100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2336200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2520500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2572600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2474600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2432900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2568700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2599200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2535300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4021,8 +4179,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,53 +4464,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1151500</v>
+      </c>
+      <c r="E72" s="3">
         <v>1035800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>958600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>898600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>789200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>586700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>453100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>465700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>391200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>313400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>241900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>239200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>277600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>207700</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,8 +4529,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,56 +4724,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3201200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3335900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3254600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3194600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3091500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3018700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2845700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2927700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2830000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2755500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2721300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2540800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2590200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2500700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2519800</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4603,8 +4789,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E81" s="3">
         <v>94400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>59400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>110100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>151800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>113600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>58500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>80000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>77300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-29900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>68900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>53700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>64200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>60500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>88100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8400</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,56 +5016,57 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E83" s="3">
         <v>21700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>19800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>26000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>22900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5600</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4880,8 +5079,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,56 +5404,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>281600</v>
+      </c>
+      <c r="E89" s="3">
         <v>32900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-33200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>180200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>306100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>159000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>301700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>53900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-50200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>124600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>258600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>62200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-56800</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5252,8 +5469,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,56 +5496,57 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-43600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-30400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27500</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5338,8 +5559,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,56 +5689,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-39800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-45400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-18400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-32200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27700</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5524,8 +5754,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5781,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5595,8 +5829,8 @@
       <c r="Q96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
+      <c r="R96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,56 +6039,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>319700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-41900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-38500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-75100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-246800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-24900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-34100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-193100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-38400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-28400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-132400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-33900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-96900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-31800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-52600</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5858,56 +6104,59 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2900</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2800</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5920,56 +6169,59 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>562300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-32000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-117200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>78900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>31000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-68300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-59300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-54100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>245000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-193500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>58000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>128800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-145400</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5980,6 +6232,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
